--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486734_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486734_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.79</v>
+        <v>2.9694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3496</v>
+        <v>0.4048</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4404</v>
+        <v>2.5645</v>
       </c>
       <c r="G2" t="n">
         <v>3.0862</v>
@@ -610,13 +610,13 @@
         <v>1.1585</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1377</v>
+        <v>0.0416</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4966</v>
+        <v>-0.4415</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3589</v>
+        <v>0.4831</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8712</v>
+        <v>2.3401</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4096</v>
+        <v>1.8785</v>
       </c>
       <c r="F3" t="n">
         <v>0.4616</v>
@@ -688,10 +688,10 @@
         <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3309</v>
+        <v>0.138</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3311</v>
+        <v>0.1378</v>
       </c>
       <c r="U3" t="n">
         <v>0.0002</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6611</v>
+        <v>2.3038</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9739</v>
+        <v>1.4428</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6872</v>
+        <v>0.861</v>
       </c>
       <c r="G4" t="n">
         <v>2.1697</v>
@@ -766,13 +766,13 @@
         <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7942</v>
+        <v>-0.1515</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4966</v>
+        <v>-0.0278</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2976</v>
+        <v>-0.1237</v>
       </c>
       <c r="V4" t="n">
         <v>0.2856</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5373</v>
+        <v>1.4435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3338</v>
+        <v>0.389</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2035</v>
+        <v>1.0545</v>
       </c>
       <c r="G5" t="n">
         <v>2.7532</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0665</v>
+        <v>-0.0274</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3863</v>
+        <v>-0.3311</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4527</v>
+        <v>0.3037</v>
       </c>
       <c r="V5" t="n">
         <v>1.2277</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>D. GARCIA NAVARO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4463</v>
+        <v>0.3473</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9</v>
+        <v>0.0866</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3463</v>
+        <v>0.2607</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9466</v>
+        <v>5.0778</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5102</v>
+        <v>3.1585</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4364</v>
+        <v>1.9193</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1792</v>
+        <v>5.5205</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6629</v>
+        <v>2.9523</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4837</v>
+        <v>2.5682</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1258</v>
+        <v>-0.4427</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1731</v>
+        <v>0.2061</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0474</v>
+        <v>-0.6489</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.4754</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.02</v>
+        <v>-4.827</v>
       </c>
       <c r="R6" t="n">
         <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8996</v>
+        <v>-0.2205</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0279</v>
+        <v>-0.607</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9275</v>
+        <v>0.3865</v>
       </c>
       <c r="V6" t="n">
-        <v>3.9687</v>
+        <v>-1.2277</v>
       </c>
       <c r="W6" t="n">
-        <v>3.9687</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1186</v>
+        <v>0.0247</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7114</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5928</v>
+        <v>-0.7418</v>
       </c>
       <c r="G7" t="n">
         <v>3.772</v>
@@ -1000,13 +1000,13 @@
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0163</v>
+        <v>-0.1101</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.607</v>
+        <v>-0.5518</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5907</v>
+        <v>0.4418</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5133</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GARCIA NAVARO</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1052</v>
+        <v>-0.0738</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0314</v>
+        <v>-0.9483</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1366</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>5.0778</v>
+        <v>-0.9466</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1585</v>
+        <v>-0.5102</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9193</v>
+        <v>-0.4364</v>
       </c>
       <c r="J8" t="n">
-        <v>5.5205</v>
+        <v>0.1792</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9523</v>
+        <v>0.6629</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5682</v>
+        <v>-0.4837</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4427</v>
+        <v>-1.1258</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2061</v>
+        <v>-1.1731</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6489</v>
+        <v>0.0474</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.2823</v>
+        <v>-3.4754</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.827</v>
+        <v>-5.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.673</v>
+        <v>0.3795</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6622</v>
+        <v>-0.0761</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0108</v>
+        <v>0.4557</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2277</v>
+        <v>3.9687</v>
       </c>
       <c r="W8" t="n">
+        <v>3.9687</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2008</v>
+        <v>-0.5043</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2212</v>
+        <v>0.1935</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0203</v>
+        <v>-0.6978</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.911</v>
+        <v>2.4816</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9517</v>
+        <v>0.7929</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0407</v>
+        <v>1.6887</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6347</v>
+        <v>3.6759</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0141</v>
+        <v>1.0694</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6488</v>
+        <v>2.6066</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2763</v>
+        <v>-1.1943</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9657</v>
+        <v>-0.2764</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6895</v>
+        <v>-0.9179</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0892</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9379</v>
+        <v>-0.2136</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4136</v>
+        <v>-0.3932</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5243</v>
+        <v>0.1796</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6138</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4983</v>
+        <v>-0.6008</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4388</v>
+        <v>-0.3728</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9405</v>
+        <v>-0.228</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8296</v>
+        <v>-0.911</v>
       </c>
       <c r="H10" t="n">
-        <v>1.214</v>
+        <v>-0.9517</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3844</v>
+        <v>0.0407</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2522</v>
+        <v>-0.6347</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0081</v>
+        <v>0.0141</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2442</v>
+        <v>-0.6488</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4226</v>
+        <v>-0.2763</v>
       </c>
       <c r="N10" t="n">
-        <v>0.206</v>
+        <v>-0.9657</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6286</v>
+        <v>0.6895</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0892</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4524</v>
+        <v>0.5379</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4409</v>
+        <v>0.2619</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0116</v>
+        <v>0.276</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0426</v>
+        <v>-0.6138</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6325</v>
+        <v>-0.785</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0901</v>
+        <v>-1.949</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7226</v>
+        <v>1.164</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4816</v>
+        <v>0.8296</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7929</v>
+        <v>1.214</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6887</v>
+        <v>-0.3844</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6759</v>
+        <v>1.2522</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0694</v>
+        <v>1.0081</v>
       </c>
       <c r="L11" t="n">
-        <v>2.6066</v>
+        <v>0.2442</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1943</v>
+        <v>-0.4226</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2764</v>
+        <v>0.206</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9179</v>
+        <v>-0.6286</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5446</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.0892</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3418</v>
+        <v>0.1658</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4966</v>
+        <v>-0.0693</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1548</v>
+        <v>0.2351</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-0.0426</v>
       </c>
       <c r="W11" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="X11" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-1.2277</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4637</v>
+        <v>-2.3892</v>
       </c>
       <c r="E12" t="n">
         <v>-0.044</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4197</v>
+        <v>-2.3452</v>
       </c>
       <c r="G12" t="n">
         <v>0.5158</v>
@@ -1390,13 +1390,13 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0607</v>
+        <v>0.0138</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1118</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.524000000000001</v>
+        <v>5.075699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2958</v>
+        <v>1.8477</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2281</v>
+        <v>3.227999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>20.0303</v>
@@ -1441,7 +1441,7 @@
         <v>9.6867</v>
       </c>
       <c r="J13" t="n">
-        <v>23.14559999999999</v>
+        <v>23.1456</v>
       </c>
       <c r="K13" t="n">
         <v>11.7292</v>
@@ -1456,7 +1456,7 @@
         <v>-1.3852</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7301</v>
+        <v>-1.730100000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-14.4807</v>
@@ -1468,13 +1468,13 @@
         <v>10.6193</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001800000000000003</v>
+        <v>0.5535000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7602</v>
+        <v>-2.208499999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.762</v>
+        <v>2.7622</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0273</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4026</v>
+        <v>3.1623</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5185</v>
+        <v>2.9036</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8841</v>
+        <v>0.2586</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.9883</v>
+        <v>1.7034</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.3651</v>
+        <v>-1.2829</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3768</v>
+        <v>2.9863</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5507</v>
+        <v>2.9384</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.7093</v>
+        <v>-0.317</v>
       </c>
       <c r="L14" t="n">
-        <v>3.26</v>
+        <v>3.2554</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.539</v>
+        <v>-1.2349</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6558</v>
+        <v>-0.9659</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8832</v>
+        <v>-0.269</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6685</v>
+        <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4489</v>
+        <v>0.0067</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3507</v>
+        <v>-0.0347</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0982</v>
+        <v>0.0414</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1698</v>
+        <v>-0.2856</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6565</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5707</v>
+        <v>1.7602</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3865</v>
+        <v>0.1741</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1841</v>
+        <v>1.5861</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7034</v>
+        <v>-1.9883</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2829</v>
+        <v>-3.3651</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9863</v>
+        <v>1.3768</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9384</v>
+        <v>1.5507</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.317</v>
+        <v>-1.7093</v>
       </c>
       <c r="L15" t="n">
-        <v>3.2554</v>
+        <v>3.26</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2349</v>
+        <v>-3.539</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9659</v>
+        <v>-1.6558</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.269</v>
+        <v>-1.8832</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7377</v>
+        <v>3.6685</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5849</v>
+        <v>0.8064</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5518</v>
+        <v>0.0062</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.033</v>
+        <v>0.8002</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2856</v>
+        <v>2.1698</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2578</v>
+        <v>1.6592</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5211</v>
+        <v>1.6246</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2634</v>
+        <v>0.0346</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3418</v>
@@ -1702,13 +1702,13 @@
         <v>3.2823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6292</v>
+        <v>-0.2278</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3314</v>
+        <v>-0.228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2977</v>
+        <v>0.0002</v>
       </c>
       <c r="V16" t="n">
         <v>1.1049</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1719</v>
+        <v>-0.4821</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6861</v>
+        <v>0.3758</v>
       </c>
       <c r="F17" t="n">
         <v>-0.858</v>
@@ -1780,10 +1780,10 @@
         <v>3.0892</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5238</v>
+        <v>0.2135</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1925</v>
+        <v>-0.1178</v>
       </c>
       <c r="U17" t="n">
         <v>0.3313</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1118</v>
+        <v>-1.5877</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6402</v>
+        <v>-1.7436</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5284</v>
+        <v>0.1559</v>
       </c>
       <c r="G18" t="n">
         <v>-3.5861</v>
@@ -1858,13 +1858,13 @@
         <v>3.2823</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4965</v>
+        <v>0.0206</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5522</v>
+        <v>-0.6556</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0486</v>
+        <v>0.6762</v>
       </c>
       <c r="V18" t="n">
         <v>0.8193</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8822</v>
+        <v>-1.6534</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2187</v>
+        <v>-1.0287</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6635</v>
+        <v>-0.6247</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.723</v>
+        <v>-3.2775</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0826</v>
+        <v>-2.1654</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6404</v>
+        <v>-1.1121</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.653</v>
+        <v>-0.4904</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6422</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2953</v>
+        <v>0.502</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.07</v>
+        <v>-2.7871</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7249</v>
+        <v>-1.173</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3451</v>
+        <v>-1.6142</v>
       </c>
       <c r="P19" t="n">
         <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6685</v>
+        <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5464</v>
+        <v>0.0136</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6349</v>
+        <v>-0.5383</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0885</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1228</v>
+        <v>-0.8995</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3505</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3236</v>
+        <v>-1.7084</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6492</v>
+        <v>-1.2187</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6744</v>
+        <v>-0.4897</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2775</v>
+        <v>-3.723</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1654</v>
+        <v>-1.0826</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1121</v>
+        <v>-2.6404</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4904</v>
+        <v>-0.653</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9923999999999999</v>
+        <v>0.6422</v>
       </c>
       <c r="L20" t="n">
-        <v>0.502</v>
+        <v>-1.2953</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7871</v>
+        <v>-3.07</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.173</v>
+        <v>-1.7249</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6142</v>
+        <v>-1.3451</v>
       </c>
       <c r="P20" t="n">
         <v>2.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R20" t="n">
-        <v>2.51</v>
+        <v>3.6685</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6566</v>
+        <v>-0.3726</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1588</v>
+        <v>-0.6349</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5022</v>
+        <v>0.2623</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8995</v>
+        <v>-0.1228</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8995</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2655</v>
+        <v>-5.6738</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8323</v>
+        <v>-4.3151</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4332</v>
+        <v>-1.3587</v>
       </c>
       <c r="G21" t="n">
         <v>-5.2473</v>
@@ -2092,13 +2092,13 @@
         <v>3.8616</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0539</v>
+        <v>-0.4623</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0761</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0223</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7366</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.523899999999999</v>
+        <v>-4.5237</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.228200000000001</v>
+        <v>-3.228000000000001</v>
       </c>
       <c r="F22" t="n">
         <v>-1.2959</v>
@@ -2170,13 +2170,13 @@
         <v>25.1001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.001800000000000024</v>
+        <v>-0.001899999999999902</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.762</v>
+        <v>-2.7621</v>
       </c>
       <c r="U22" t="n">
-        <v>2.7604</v>
+        <v>2.7602</v>
       </c>
       <c r="V22" t="n">
         <v>1.0273</v>
